--- a/cp-typo-narratif-num-flux/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/cp-typo-narratif-num-flux/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:00:53+00:00</t>
+    <t>2026-03-04T13:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
